--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.66111578927981</v>
+        <v>25.66018793510855</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.18694586121584</v>
+        <v>26.17170279424677</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.87237068137576</v>
+        <v>24.89291564640121</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.226305234594651</v>
+        <v>1.22634486751521</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28968.78703702468</v>
+        <v>28968.40521714127</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.299185439750229</v>
+        <v>1.299365830488089</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1567.738105125783</v>
+        <v>1565.948089897804</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3075.170630749888</v>
+        <v>3073.380615521908</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.18694586121584</v>
+        <v>26.17170279424677</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.18694586121584</v>
+        <v>26.17170279424677</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.12174029141031</v>
+        <v>22.14772286156301</v>
       </c>
       <c r="F11" t="n">
-        <v>17.49212560259212</v>
+        <v>17.51267056761757</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.87237068137576</v>
+        <v>24.89291564640121</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.4056631054056</v>
+        <v>18.40492082206859</v>
       </c>
       <c r="C2" t="n">
-        <v>21.26185246412345</v>
+        <v>21.26101739536931</v>
       </c>
       <c r="D2" t="n">
-        <v>24.11804182284123</v>
+        <v>24.11711396866997</v>
       </c>
       <c r="E2" t="n">
-        <v>26.97423118155901</v>
+        <v>26.97321054197062</v>
       </c>
       <c r="F2" t="n">
-        <v>29.8304205402768</v>
+        <v>29.82930711527131</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.17720008862489</v>
+        <v>19.17645780528788</v>
       </c>
       <c r="C3" t="n">
-        <v>22.03338944734273</v>
+        <v>22.03255437858861</v>
       </c>
       <c r="D3" t="n">
-        <v>24.88957880606052</v>
+        <v>24.88865095188926</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7457681647783</v>
+        <v>27.74474752518991</v>
       </c>
       <c r="F3" t="n">
-        <v>30.6019575234961</v>
+        <v>30.60084409849059</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.94873707184418</v>
+        <v>19.94799478850717</v>
       </c>
       <c r="C4" t="n">
-        <v>22.80492643056203</v>
+        <v>22.8040913618079</v>
       </c>
       <c r="D4" t="n">
-        <v>25.66111578927981</v>
+        <v>25.66018793510855</v>
       </c>
       <c r="E4" t="n">
-        <v>28.51730514799759</v>
+        <v>28.5162845084092</v>
       </c>
       <c r="F4" t="n">
-        <v>31.37349450671539</v>
+        <v>31.37238108170989</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.72027405506347</v>
+        <v>20.71953177172646</v>
       </c>
       <c r="C5" t="n">
-        <v>23.57646341378132</v>
+        <v>23.57562834502719</v>
       </c>
       <c r="D5" t="n">
-        <v>26.4326527724991</v>
+        <v>26.43172491832784</v>
       </c>
       <c r="E5" t="n">
-        <v>29.28884213121688</v>
+        <v>29.28782149162849</v>
       </c>
       <c r="F5" t="n">
-        <v>32.14503148993468</v>
+        <v>32.14391806492918</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.49181103828276</v>
+        <v>21.49106875494575</v>
       </c>
       <c r="C6" t="n">
-        <v>24.34800039700061</v>
+        <v>24.34716532824648</v>
       </c>
       <c r="D6" t="n">
-        <v>27.20418975571839</v>
+        <v>27.20326190154713</v>
       </c>
       <c r="E6" t="n">
-        <v>30.06037911443617</v>
+        <v>30.05935847484778</v>
       </c>
       <c r="F6" t="n">
-        <v>32.91656847315397</v>
+        <v>32.91545504814847</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.66018793510855</v>
+        <v>25.74132005035982</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.17170279424677</v>
+        <v>26.26582682376601</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.89291564640121</v>
+        <v>24.95455989025054</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.22634486751521</v>
+        <v>1.226125526858709</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28968.40521714127</v>
+        <v>28583.42000949432</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.299365830488089</v>
+        <v>1.283592358117507</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1565.948089897804</v>
+        <v>1563.32235573113</v>
       </c>
     </row>
     <row r="3">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1300.542097238288</v>
+        <v>1314.220951259388</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3073.380615521908</v>
+        <v>3084.433735376335</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.17170279424677</v>
+        <v>26.26582682376601</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.17170279424677</v>
+        <v>26.26582682376601</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.14772286156301</v>
+        <v>22.22568239511982</v>
       </c>
       <c r="F11" t="n">
-        <v>17.51267056761757</v>
+        <v>17.57431481146689</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.89291564640121</v>
+        <v>24.95455989025054</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.40492082206859</v>
+        <v>18.46982651426962</v>
       </c>
       <c r="C2" t="n">
-        <v>21.26101739536931</v>
+        <v>21.33403629909544</v>
       </c>
       <c r="D2" t="n">
-        <v>24.11711396866997</v>
+        <v>24.19824608392124</v>
       </c>
       <c r="E2" t="n">
-        <v>26.97321054197062</v>
+        <v>27.06245586874707</v>
       </c>
       <c r="F2" t="n">
-        <v>29.82930711527131</v>
+        <v>29.92666565357283</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.17645780528788</v>
+        <v>19.24136349748891</v>
       </c>
       <c r="C3" t="n">
-        <v>22.03255437858861</v>
+        <v>22.10557328231474</v>
       </c>
       <c r="D3" t="n">
-        <v>24.88865095188926</v>
+        <v>24.96978306714053</v>
       </c>
       <c r="E3" t="n">
-        <v>27.74474752518991</v>
+        <v>27.83399285196635</v>
       </c>
       <c r="F3" t="n">
-        <v>30.60084409849059</v>
+        <v>30.69820263679212</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.94799478850717</v>
+        <v>20.0129004807082</v>
       </c>
       <c r="C4" t="n">
-        <v>22.8040913618079</v>
+        <v>22.87711026553403</v>
       </c>
       <c r="D4" t="n">
-        <v>25.66018793510855</v>
+        <v>25.74132005035982</v>
       </c>
       <c r="E4" t="n">
-        <v>28.5162845084092</v>
+        <v>28.60552983518564</v>
       </c>
       <c r="F4" t="n">
-        <v>31.37238108170989</v>
+        <v>31.46973962001141</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.71953177172646</v>
+        <v>20.7844374639275</v>
       </c>
       <c r="C5" t="n">
-        <v>23.57562834502719</v>
+        <v>23.64864724875332</v>
       </c>
       <c r="D5" t="n">
-        <v>26.43172491832784</v>
+        <v>26.51285703357911</v>
       </c>
       <c r="E5" t="n">
-        <v>29.28782149162849</v>
+        <v>29.37706681840493</v>
       </c>
       <c r="F5" t="n">
-        <v>32.14391806492918</v>
+        <v>32.2412766032307</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.49106875494575</v>
+        <v>21.55597444714679</v>
       </c>
       <c r="C6" t="n">
-        <v>24.34716532824648</v>
+        <v>24.42018423197261</v>
       </c>
       <c r="D6" t="n">
-        <v>27.20326190154713</v>
+        <v>27.2843940167984</v>
       </c>
       <c r="E6" t="n">
-        <v>30.05935847484778</v>
+        <v>30.14860380162423</v>
       </c>
       <c r="F6" t="n">
-        <v>32.91545504814847</v>
+        <v>33.01281358644999</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.19</v>
+        <v>25.28</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.66</v>
+        <v>25.74</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.82</v>
+        <v>25.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.2</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28583.42000949432</v>
+        <v>25855.9365343715</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.283592358117507</v>
+        <v>1.161109571089344</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.57</v>
+        <v>27.06</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25855.9365343715</v>
+        <v>27977.31257057813</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.161109571089344</v>
+        <v>1.256373961000138</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.06</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27977.31257057813</v>
+        <v>28366.95306702425</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.256373961000138</v>
+        <v>1.273871502004161</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.74132005035982</v>
+        <v>26.0030367127697</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.26582682376601</v>
+        <v>26.5739675863085</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.95455989025054</v>
+        <v>25.1466404024615</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.226125526858709</v>
+        <v>1.228031408721838</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28366.95306702425</v>
+        <v>27187.22975327548</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.273871502004161</v>
+        <v>1.222989301649128</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>956.9944283858197</v>
+        <v>988.6180481235031</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1314.220951259388</v>
+        <v>1318.782743449062</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3084.433735376335</v>
+        <v>3120.619147303694</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.26582682376601</v>
+        <v>26.5739675863085</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.26582682376601</v>
+        <v>26.5739675863085</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.22568239511982</v>
+        <v>22.4686005688575</v>
       </c>
       <c r="F11" t="n">
-        <v>17.57431481146689</v>
+        <v>17.76639532367786</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.95455989025054</v>
+        <v>25.1466404024615</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.46982651426962</v>
+        <v>18.67919984419758</v>
       </c>
       <c r="C2" t="n">
-        <v>21.33403629909544</v>
+        <v>21.56958129526436</v>
       </c>
       <c r="D2" t="n">
-        <v>24.19824608392124</v>
+        <v>24.45996274633112</v>
       </c>
       <c r="E2" t="n">
-        <v>27.06245586874707</v>
+        <v>27.35034419739791</v>
       </c>
       <c r="F2" t="n">
-        <v>29.92666565357283</v>
+        <v>30.24072564846475</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.24136349748891</v>
+        <v>19.45073682741687</v>
       </c>
       <c r="C3" t="n">
-        <v>22.10557328231474</v>
+        <v>22.34111827848365</v>
       </c>
       <c r="D3" t="n">
-        <v>24.96978306714053</v>
+        <v>25.23149972955041</v>
       </c>
       <c r="E3" t="n">
-        <v>27.83399285196635</v>
+        <v>28.1218811806172</v>
       </c>
       <c r="F3" t="n">
-        <v>30.69820263679212</v>
+        <v>31.01226263168404</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.0129004807082</v>
+        <v>20.22227381063616</v>
       </c>
       <c r="C4" t="n">
-        <v>22.87711026553403</v>
+        <v>23.11265526170294</v>
       </c>
       <c r="D4" t="n">
-        <v>25.74132005035982</v>
+        <v>26.0030367127697</v>
       </c>
       <c r="E4" t="n">
-        <v>28.60552983518564</v>
+        <v>28.89341816383649</v>
       </c>
       <c r="F4" t="n">
-        <v>31.46973962001141</v>
+        <v>31.78379961490333</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.7844374639275</v>
+        <v>20.99381079385545</v>
       </c>
       <c r="C5" t="n">
-        <v>23.64864724875332</v>
+        <v>23.88419224492223</v>
       </c>
       <c r="D5" t="n">
-        <v>26.51285703357911</v>
+        <v>26.77457369598899</v>
       </c>
       <c r="E5" t="n">
-        <v>29.37706681840493</v>
+        <v>29.66495514705579</v>
       </c>
       <c r="F5" t="n">
-        <v>32.2412766032307</v>
+        <v>32.55533659812262</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.55597444714679</v>
+        <v>21.76534777707474</v>
       </c>
       <c r="C6" t="n">
-        <v>24.42018423197261</v>
+        <v>24.65572922814152</v>
       </c>
       <c r="D6" t="n">
-        <v>27.2843940167984</v>
+        <v>27.54611067920828</v>
       </c>
       <c r="E6" t="n">
-        <v>30.14860380162423</v>
+        <v>30.43649213027507</v>
       </c>
       <c r="F6" t="n">
-        <v>33.01281358644999</v>
+        <v>33.32687358134191</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.28</v>
+        <v>25.54</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.74</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.9</v>
+        <v>26.16</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.15</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27187.22975327548</v>
+        <v>21395.85580450506</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.222989301649128</v>
+        <v>0.9624703578114473</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.0030367127697</v>
+        <v>25.68297056238972</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25.1466404024615</v>
+        <v>24.34647502651154</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21395.85580450506</v>
+        <v>22754.81214504832</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9624703578114473</v>
+        <v>1.023601597771356</v>
       </c>
     </row>
   </sheetData>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>22.4686005688575</v>
+        <v>21.45665662110078</v>
       </c>
       <c r="F11" t="n">
-        <v>17.76639532367786</v>
+        <v>16.9662299477279</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>25.1466404024615</v>
+        <v>24.34647502651154</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.67919984419758</v>
+        <v>18.37880478290071</v>
       </c>
       <c r="C2" t="n">
-        <v>21.56958129526436</v>
+        <v>21.2235518377524</v>
       </c>
       <c r="D2" t="n">
-        <v>24.45996274633112</v>
+        <v>24.06829889260407</v>
       </c>
       <c r="E2" t="n">
-        <v>27.35034419739791</v>
+        <v>26.91304594745577</v>
       </c>
       <c r="F2" t="n">
-        <v>30.24072564846475</v>
+        <v>29.75779300230752</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.45073682741687</v>
+        <v>19.18614061779353</v>
       </c>
       <c r="C3" t="n">
-        <v>22.34111827848365</v>
+        <v>22.03088767264523</v>
       </c>
       <c r="D3" t="n">
-        <v>25.23149972955041</v>
+        <v>24.87563472749689</v>
       </c>
       <c r="E3" t="n">
-        <v>28.1218811806172</v>
+        <v>27.7203817823486</v>
       </c>
       <c r="F3" t="n">
-        <v>31.01226263168404</v>
+        <v>30.56512883720034</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.22227381063616</v>
+        <v>19.99347645268636</v>
       </c>
       <c r="C4" t="n">
-        <v>23.11265526170294</v>
+        <v>22.83822350753805</v>
       </c>
       <c r="D4" t="n">
-        <v>26.0030367127697</v>
+        <v>25.68297056238972</v>
       </c>
       <c r="E4" t="n">
-        <v>28.89341816383649</v>
+        <v>28.52771761724141</v>
       </c>
       <c r="F4" t="n">
-        <v>31.78379961490333</v>
+        <v>31.37246467209317</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.99381079385545</v>
+        <v>20.80081228757918</v>
       </c>
       <c r="C5" t="n">
-        <v>23.88419224492223</v>
+        <v>23.64555934243088</v>
       </c>
       <c r="D5" t="n">
-        <v>26.77457369598899</v>
+        <v>26.49030639728254</v>
       </c>
       <c r="E5" t="n">
-        <v>29.66495514705579</v>
+        <v>29.33505345213424</v>
       </c>
       <c r="F5" t="n">
-        <v>32.55533659812262</v>
+        <v>32.17980050698599</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.76534777707474</v>
+        <v>21.60814812247201</v>
       </c>
       <c r="C6" t="n">
-        <v>24.65572922814152</v>
+        <v>24.4528951773237</v>
       </c>
       <c r="D6" t="n">
-        <v>27.54611067920828</v>
+        <v>27.29764223217536</v>
       </c>
       <c r="E6" t="n">
-        <v>30.43649213027507</v>
+        <v>30.14238928702706</v>
       </c>
       <c r="F6" t="n">
-        <v>33.32687358134191</v>
+        <v>32.98713634187882</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.54</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>25.68</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.16</v>
+        <v>25.7</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.81</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22754.81214504832</v>
+        <v>16931.1195669162</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.023601597771356</v>
+        <v>0.7616288339486308</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.68297056238972</v>
+        <v>25.99893115471696</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.5739675863085</v>
+        <v>26.90953477118632</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.34647502651154</v>
+        <v>24.63302573001291</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.228031408721838</v>
+        <v>1.230010127943657</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16931.1195669162</v>
+        <v>15583.42373483202</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7616288339486308</v>
+        <v>0.7029245292457706</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1563.32235573113</v>
+        <v>1557.497645946201</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>988.6180481235031</v>
+        <v>1022.242394433771</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1318.782743449062</v>
+        <v>1330.389242982839</v>
       </c>
     </row>
     <row r="5">
@@ -723,7 +723,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3120.619147303694</v>
+        <v>3160.025283362806</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.5739675863085</v>
+        <v>26.90953477118632</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.5739675863085</v>
+        <v>26.90953477118632</v>
       </c>
     </row>
     <row r="15">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.45665662110078</v>
+        <v>21.8190482701888</v>
       </c>
       <c r="F11" t="n">
-        <v>16.9662299477279</v>
+        <v>17.25278065122927</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.34647502651154</v>
+        <v>24.63302573001291</v>
       </c>
     </row>
     <row r="13">
@@ -1100,19 +1100,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.37880478290071</v>
+        <v>18.63157325676249</v>
       </c>
       <c r="C2" t="n">
-        <v>21.2235518377524</v>
+        <v>21.50791637084692</v>
       </c>
       <c r="D2" t="n">
-        <v>24.06829889260407</v>
+        <v>24.38425948493131</v>
       </c>
       <c r="E2" t="n">
-        <v>26.91304594745577</v>
+        <v>27.26060259901575</v>
       </c>
       <c r="F2" t="n">
-        <v>29.75779300230752</v>
+        <v>30.1369457131002</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1122,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.18614061779353</v>
+        <v>19.43890909165531</v>
       </c>
       <c r="C3" t="n">
-        <v>22.03088767264523</v>
+        <v>22.31525220573974</v>
       </c>
       <c r="D3" t="n">
-        <v>24.87563472749689</v>
+        <v>25.19159531982413</v>
       </c>
       <c r="E3" t="n">
-        <v>27.7203817823486</v>
+        <v>28.06793843390858</v>
       </c>
       <c r="F3" t="n">
-        <v>30.56512883720034</v>
+        <v>30.94428154799303</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1144,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.99347645268636</v>
+        <v>20.24624492654814</v>
       </c>
       <c r="C4" t="n">
-        <v>22.83822350753805</v>
+        <v>23.12258804063256</v>
       </c>
       <c r="D4" t="n">
-        <v>25.68297056238972</v>
+        <v>25.99893115471696</v>
       </c>
       <c r="E4" t="n">
-        <v>28.52771761724141</v>
+        <v>28.87527426880141</v>
       </c>
       <c r="F4" t="n">
-        <v>31.37246467209317</v>
+        <v>31.75161738288585</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20.80081228757918</v>
+        <v>21.05358076144096</v>
       </c>
       <c r="C5" t="n">
-        <v>23.64555934243088</v>
+        <v>23.92992387552539</v>
       </c>
       <c r="D5" t="n">
-        <v>26.49030639728254</v>
+        <v>26.80626698960979</v>
       </c>
       <c r="E5" t="n">
-        <v>29.33505345213424</v>
+        <v>29.68261010369423</v>
       </c>
       <c r="F5" t="n">
-        <v>32.17980050698599</v>
+        <v>32.55895321777868</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.60814812247201</v>
+        <v>21.86091659633379</v>
       </c>
       <c r="C6" t="n">
-        <v>24.4528951773237</v>
+        <v>24.73725971041821</v>
       </c>
       <c r="D6" t="n">
-        <v>27.29764223217536</v>
+        <v>27.61360282450261</v>
       </c>
       <c r="E6" t="n">
-        <v>30.14238928702706</v>
+        <v>30.48994593858706</v>
       </c>
       <c r="F6" t="n">
-        <v>32.98713634187882</v>
+        <v>33.3662890526715</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1238,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.63</v>
+        <v>25.94</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1246,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>25.68</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>25.7</v>
+        <v>26.02</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.4</v>
+        <v>24.64</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15583.42373483202</v>
+        <v>16571.98241122546</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7029245292457706</v>
+        <v>0.747515637981554</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.99893115471696</v>
+        <v>28.34048408242711</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.90953477118632</v>
+        <v>29.34138963654237</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.63302573001291</v>
+        <v>26.83912575125421</v>
       </c>
     </row>
     <row r="9">
@@ -542,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.230010127943657</v>
+        <v>1.252458353575725</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16571.98241122546</v>
+        <v>7455.213369190578</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.747515637981554</v>
+        <v>0.3414340412253809</v>
       </c>
     </row>
   </sheetData>
@@ -644,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1022.242394433771</v>
+        <v>1407.817600984264</v>
       </c>
     </row>
     <row r="4">
@@ -714,7 +713,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99.999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3160.025283362806</v>
+        <v>3445.6014899133</v>
       </c>
     </row>
     <row r="12">
@@ -743,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.90953477118632</v>
+        <v>29.34138963654237</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.90953477118632</v>
+        <v>29.34138963654237</v>
       </c>
     </row>
     <row r="15">
@@ -833,13 +832,13 @@
         <v>31200</v>
       </c>
       <c r="D2" t="n">
-        <v>1.497521383435364</v>
+        <v>1.593623717533555</v>
       </c>
       <c r="E2" t="n">
-        <v>1.422645314263596</v>
+        <v>1.513942531656877</v>
       </c>
       <c r="F2" t="n">
-        <v>1.386008498065798</v>
+        <v>1.474954574707782</v>
       </c>
     </row>
     <row r="3">
@@ -855,13 +854,13 @@
         <v>31450</v>
       </c>
       <c r="D3" t="n">
-        <v>1.391405216584469</v>
+        <v>1.479740167102616</v>
       </c>
       <c r="E3" t="n">
-        <v>1.321834955755246</v>
+        <v>1.405753158747485</v>
       </c>
       <c r="F3" t="n">
-        <v>1.254630217320242</v>
+        <v>1.334281850679508</v>
       </c>
     </row>
     <row r="4">
@@ -877,13 +876,13 @@
         <v>28500</v>
       </c>
       <c r="D4" t="n">
-        <v>1.112731292945539</v>
+        <v>1.185836079581247</v>
       </c>
       <c r="E4" t="n">
-        <v>1.057094728298262</v>
+        <v>1.126544275602184</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9775110443094059</v>
+        <v>1.041732062250873</v>
       </c>
     </row>
     <row r="5">
@@ -899,13 +898,13 @@
         <v>27000</v>
       </c>
       <c r="D5" t="n">
-        <v>1.033305988298619</v>
+        <v>1.103364742157839</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9816406888836876</v>
+        <v>1.048196505049947</v>
       </c>
       <c r="F5" t="n">
-        <v>0.884360980976295</v>
+        <v>0.9443211757206725</v>
       </c>
     </row>
     <row r="6">
@@ -921,13 +920,13 @@
         <v>25500</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9557083033175913</v>
+        <v>1.021502611289728</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9079228881517116</v>
+        <v>0.9704274807252419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7968842458355274</v>
+        <v>0.8517445492425847</v>
       </c>
     </row>
     <row r="7">
@@ -943,13 +942,13 @@
         <v>25000</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9166429329591348</v>
+        <v>0.9800004147100817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.870810786311178</v>
+        <v>0.9310003939745776</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7446279464997976</v>
+        <v>0.796095917107835</v>
       </c>
     </row>
     <row r="8">
@@ -965,13 +964,13 @@
         <v>24500</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8705716872147564</v>
+        <v>0.9302739296339179</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8270431028540186</v>
+        <v>0.883760233152222</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6889900201606276</v>
+        <v>0.7362397180454907</v>
       </c>
     </row>
     <row r="9">
@@ -987,13 +986,13 @@
         <v>24000</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8394260020751684</v>
+        <v>0.8973006248284371</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7974547019714099</v>
+        <v>0.8524355935870152</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6472321256159482</v>
+        <v>0.6918558506509334</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.380245078783641</v>
+        <v>7.871225698405679</v>
       </c>
     </row>
     <row r="11">
@@ -1013,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.8190482701888</v>
+        <v>23.98810575544708</v>
       </c>
       <c r="F11" t="n">
-        <v>17.25278065122927</v>
+        <v>18.96790005284853</v>
       </c>
     </row>
     <row r="12">
@@ -1026,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.63302573001291</v>
+        <v>26.83912575125421</v>
       </c>
     </row>
     <row r="13">
@@ -1057,7 +1056,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1100,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.63157325676249</v>
+        <v>20.30231183647797</v>
       </c>
       <c r="C2" t="n">
-        <v>21.50791637084692</v>
+        <v>23.47028949403538</v>
       </c>
       <c r="D2" t="n">
-        <v>24.38425948493131</v>
+        <v>26.63826715159275</v>
       </c>
       <c r="E2" t="n">
-        <v>27.26060259901575</v>
+        <v>29.80624480915018</v>
       </c>
       <c r="F2" t="n">
-        <v>30.1369457131002</v>
+        <v>32.97422246670762</v>
       </c>
     </row>
     <row r="3">
@@ -1122,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19.43890909165531</v>
+        <v>21.15342030189515</v>
       </c>
       <c r="C3" t="n">
-        <v>22.31525220573974</v>
+        <v>24.32139795945256</v>
       </c>
       <c r="D3" t="n">
-        <v>25.19159531982413</v>
+        <v>27.48937561700993</v>
       </c>
       <c r="E3" t="n">
-        <v>28.06793843390858</v>
+        <v>30.65735327456736</v>
       </c>
       <c r="F3" t="n">
-        <v>30.94428154799303</v>
+        <v>33.82533093212479</v>
       </c>
     </row>
     <row r="4">
@@ -1144,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20.24624492654814</v>
+        <v>22.00452876731233</v>
       </c>
       <c r="C4" t="n">
-        <v>23.12258804063256</v>
+        <v>25.17250642486974</v>
       </c>
       <c r="D4" t="n">
-        <v>25.99893115471696</v>
+        <v>28.34048408242711</v>
       </c>
       <c r="E4" t="n">
-        <v>28.87527426880141</v>
+        <v>31.50846173998454</v>
       </c>
       <c r="F4" t="n">
-        <v>31.75161738288585</v>
+        <v>34.67643939754198</v>
       </c>
     </row>
     <row r="5">
@@ -1166,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.05358076144096</v>
+        <v>22.85563723272951</v>
       </c>
       <c r="C5" t="n">
-        <v>23.92992387552539</v>
+        <v>26.02361489028691</v>
       </c>
       <c r="D5" t="n">
-        <v>26.80626698960979</v>
+        <v>29.19159254784429</v>
       </c>
       <c r="E5" t="n">
-        <v>29.68261010369423</v>
+        <v>32.35957020540172</v>
       </c>
       <c r="F5" t="n">
-        <v>32.55895321777868</v>
+        <v>35.52754786295915</v>
       </c>
     </row>
     <row r="6">
@@ -1188,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.86091659633379</v>
+        <v>23.70674569814668</v>
       </c>
       <c r="C6" t="n">
-        <v>24.73725971041821</v>
+        <v>26.8747233557041</v>
       </c>
       <c r="D6" t="n">
-        <v>27.61360282450261</v>
+        <v>30.04270101326147</v>
       </c>
       <c r="E6" t="n">
-        <v>30.48994593858706</v>
+        <v>33.2106786708189</v>
       </c>
       <c r="F6" t="n">
-        <v>33.3662890526715</v>
+        <v>36.37865632837633</v>
       </c>
     </row>
   </sheetData>
@@ -1238,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.94</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="3">
@@ -1246,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>28.34</v>
       </c>
     </row>
     <row r="4">
@@ -1254,38 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.02</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
+        <v>28.36</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.64</v>
+        <v>24.97</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7455.213369190578</v>
+        <v>8818.538582407251</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3414340412253809</v>
+        <v>0.403871642136535</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.97</v>
+        <v>24.81</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8818.538582407251</v>
+        <v>8164.459663496271</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.403871642136535</v>
+        <v>0.3739161200736768</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.34048408242711</v>
+        <v>28.31757147431574</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.83912575125421</v>
+        <v>26.78184423097578</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27000</v>
+        <v>33100</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.252458353575725</v>
+        <v>1.416836670288062</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8164.459663496271</v>
+        <v>8258.779758915269</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3739161200736768</v>
+        <v>0.3756205020422172</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="C2" t="n">
-        <v>31200</v>
+        <v>32500</v>
       </c>
       <c r="D2" t="n">
-        <v>1.593623717533555</v>
+        <v>1.528134012839067</v>
       </c>
       <c r="E2" t="n">
-        <v>1.513942531656877</v>
+        <v>1.451727312197113</v>
       </c>
       <c r="F2" t="n">
-        <v>1.474954574707782</v>
+        <v>1.414341558929568</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>31450</v>
+        <v>33650</v>
       </c>
       <c r="C3" t="n">
-        <v>31450</v>
+        <v>33650</v>
       </c>
       <c r="D3" t="n">
-        <v>1.479740167102616</v>
+        <v>1.46409117371341</v>
       </c>
       <c r="E3" t="n">
-        <v>1.405753158747485</v>
+        <v>1.390886615027739</v>
       </c>
       <c r="F3" t="n">
-        <v>1.334281850679508</v>
+        <v>1.320171151838707</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="C4" t="n">
-        <v>28500</v>
+        <v>29500</v>
       </c>
       <c r="D4" t="n">
-        <v>1.185836079581247</v>
+        <v>1.192994256605993</v>
       </c>
       <c r="E4" t="n">
-        <v>1.126544275602184</v>
+        <v>1.133344543775693</v>
       </c>
       <c r="F4" t="n">
-        <v>1.041732062250873</v>
+        <v>1.048020370257641</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="C5" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="D5" t="n">
-        <v>1.103364742157839</v>
+        <v>1.118214151943217</v>
       </c>
       <c r="E5" t="n">
-        <v>1.048196505049947</v>
+        <v>1.062303444346056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9443211757206725</v>
+        <v>0.9570301300414917</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25500</v>
+        <v>27500</v>
       </c>
       <c r="C6" t="n">
-        <v>25500</v>
+        <v>27500</v>
       </c>
       <c r="D6" t="n">
-        <v>1.021502611289728</v>
+        <v>1.043434047280441</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9704274807252419</v>
+        <v>0.9912623449164185</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8517445492425847</v>
+        <v>0.870031317044937</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="C7" t="n">
-        <v>25000</v>
+        <v>26500</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9800004147100817</v>
+        <v>0.9686539426176645</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9310003939745776</v>
+        <v>0.9202212454867812</v>
       </c>
       <c r="F7" t="n">
-        <v>0.796095917107835</v>
+        <v>0.7868786964100013</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24500</v>
+        <v>26000</v>
       </c>
       <c r="C8" t="n">
-        <v>24500</v>
+        <v>26000</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9302739296339179</v>
+        <v>0.9271517460380179</v>
       </c>
       <c r="E8" t="n">
-        <v>0.883760233152222</v>
+        <v>0.8807941587361169</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7362397180454907</v>
+        <v>0.733768751702022</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="C9" t="n">
-        <v>24000</v>
+        <v>25500</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8973006248284371</v>
+        <v>0.8897616937066297</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8524355935870152</v>
+        <v>0.8452736090212982</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6918558506509334</v>
+        <v>0.6860430233108499</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.871225698405679</v>
+        <v>7.816284999535219</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.98810575544708</v>
+        <v>23.98514539234243</v>
       </c>
       <c r="F11" t="n">
-        <v>18.96790005284853</v>
+        <v>18.96555923144056</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26.83912575125421</v>
+        <v>26.78184423097578</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29537.5</v>
+        <v>31037.5</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1056,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.30231183647797</v>
+        <v>20.2862730108</v>
       </c>
       <c r="C2" t="n">
-        <v>23.47028949403538</v>
+        <v>23.45425066835742</v>
       </c>
       <c r="D2" t="n">
-        <v>26.63826715159275</v>
+        <v>26.62222832591479</v>
       </c>
       <c r="E2" t="n">
-        <v>29.80624480915018</v>
+        <v>29.79020598347222</v>
       </c>
       <c r="F2" t="n">
-        <v>32.97422246670762</v>
+        <v>32.95818364102965</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.15342030189515</v>
+        <v>21.13394458500048</v>
       </c>
       <c r="C3" t="n">
-        <v>24.32139795945256</v>
+        <v>24.30192224255789</v>
       </c>
       <c r="D3" t="n">
-        <v>27.48937561700993</v>
+        <v>27.46989990011526</v>
       </c>
       <c r="E3" t="n">
-        <v>30.65735327456736</v>
+        <v>30.63787755767269</v>
       </c>
       <c r="F3" t="n">
-        <v>33.82533093212479</v>
+        <v>33.80585521523012</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.00452876731233</v>
+        <v>21.98161615920095</v>
       </c>
       <c r="C4" t="n">
-        <v>25.17250642486974</v>
+        <v>25.14959381675836</v>
       </c>
       <c r="D4" t="n">
-        <v>28.34048408242711</v>
+        <v>28.31757147431574</v>
       </c>
       <c r="E4" t="n">
-        <v>31.50846173998454</v>
+        <v>31.48554913187316</v>
       </c>
       <c r="F4" t="n">
-        <v>34.67643939754198</v>
+        <v>34.6535267894306</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.85563723272951</v>
+        <v>22.82928773340143</v>
       </c>
       <c r="C5" t="n">
-        <v>26.02361489028691</v>
+        <v>25.99726539095884</v>
       </c>
       <c r="D5" t="n">
-        <v>29.19159254784429</v>
+        <v>29.16524304851621</v>
       </c>
       <c r="E5" t="n">
-        <v>32.35957020540172</v>
+        <v>32.33322070607364</v>
       </c>
       <c r="F5" t="n">
-        <v>35.52754786295915</v>
+        <v>35.50119836363108</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.70674569814668</v>
+        <v>23.6769593076019</v>
       </c>
       <c r="C6" t="n">
-        <v>26.8747233557041</v>
+        <v>26.84493696515931</v>
       </c>
       <c r="D6" t="n">
-        <v>30.04270101326147</v>
+        <v>30.01291462271668</v>
       </c>
       <c r="E6" t="n">
-        <v>33.2106786708189</v>
+        <v>33.18089228027411</v>
       </c>
       <c r="F6" t="n">
-        <v>36.37865632837633</v>
+        <v>36.34886993783154</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>28.28</v>
+        <v>28.26</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>28.34</v>
+        <v>28.32</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>28.36</v>
+        <v>28.34</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.81</v>
+        <v>25.15</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8258.779758915269</v>
+        <v>9650.305621008123</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3756205020422172</v>
+        <v>0.4389089851089575</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.15</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9650.305621008123</v>
+        <v>12503.11764797876</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4389089851089575</v>
+        <v>0.5686587444055449</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.88</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12503.11764797876</v>
+        <v>14331.75713319435</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5686587444055449</v>
+        <v>0.6518277477621761</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.31757147431574</v>
+        <v>28.49724764445898</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.78184423097578</v>
+        <v>27.2310346563339</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33100</v>
+        <v>35300</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.416836670288062</v>
+        <v>1.486770770757503</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14331.75713319435</v>
+        <v>14427.13661050425</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6518277477621761</v>
+        <v>0.6317417369869784</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>32500</v>
+        <v>35400</v>
       </c>
       <c r="C2" t="n">
-        <v>32500</v>
+        <v>35400</v>
       </c>
       <c r="D2" t="n">
-        <v>1.528134012839067</v>
+        <v>1.636420478043209</v>
       </c>
       <c r="E2" t="n">
-        <v>1.451727312197113</v>
+        <v>1.554599454141048</v>
       </c>
       <c r="F2" t="n">
-        <v>1.414341558929568</v>
+        <v>1.514564475716336</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33650</v>
+        <v>35200</v>
       </c>
       <c r="C3" t="n">
-        <v>33650</v>
+        <v>35200</v>
       </c>
       <c r="D3" t="n">
-        <v>1.46409117371341</v>
+        <v>1.572339563507846</v>
       </c>
       <c r="E3" t="n">
-        <v>1.390886615027739</v>
+        <v>1.493722585332454</v>
       </c>
       <c r="F3" t="n">
-        <v>1.320171151838707</v>
+        <v>1.417778735304393</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="C4" t="n">
-        <v>29500</v>
+        <v>30100</v>
       </c>
       <c r="D4" t="n">
-        <v>1.192994256605993</v>
+        <v>1.2398650859542</v>
       </c>
       <c r="E4" t="n">
-        <v>1.133344543775693</v>
+        <v>1.17787183165649</v>
       </c>
       <c r="F4" t="n">
-        <v>1.048020370257641</v>
+        <v>1.089195408323238</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="C5" t="n">
-        <v>28500</v>
+        <v>29100</v>
       </c>
       <c r="D5" t="n">
-        <v>1.118214151943217</v>
+        <v>1.165084981291423</v>
       </c>
       <c r="E5" t="n">
-        <v>1.062303444346056</v>
+        <v>1.106830732226852</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9570301300414917</v>
+        <v>0.9971448038079749</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="C6" t="n">
-        <v>27500</v>
+        <v>28100</v>
       </c>
       <c r="D6" t="n">
-        <v>1.043434047280441</v>
+        <v>1.090304876628647</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9912623449164185</v>
+        <v>1.035789632797215</v>
       </c>
       <c r="F6" t="n">
-        <v>0.870031317044937</v>
+        <v>0.9091129336503116</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="C7" t="n">
-        <v>26500</v>
+        <v>27100</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9686539426176645</v>
+        <v>1.015524771965871</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9202212454867812</v>
+        <v>0.9647485333675773</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7868786964100013</v>
+        <v>0.8249538597624616</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="C8" t="n">
-        <v>26000</v>
+        <v>26600</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9271517460380179</v>
+        <v>0.9740225753862243</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8807941587361169</v>
+        <v>0.9253214466169131</v>
       </c>
       <c r="F8" t="n">
-        <v>0.733768751702022</v>
+        <v>0.7708633805899471</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="C9" t="n">
-        <v>25500</v>
+        <v>26100</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8897616937066297</v>
+        <v>0.9366325230548362</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8452736090212982</v>
+        <v>0.8898008969020944</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6860430233108499</v>
+        <v>0.7221823690464202</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7.816284999535219</v>
+        <v>8.245795966201083</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>23.98514539234243</v>
+        <v>24.01003338389682</v>
       </c>
       <c r="F11" t="n">
-        <v>18.96555923144056</v>
+        <v>18.98523869013281</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>26.78184423097578</v>
+        <v>27.2310346563339</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31037.5</v>
+        <v>32450</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.2862730108</v>
+        <v>20.41204632990028</v>
       </c>
       <c r="C2" t="n">
-        <v>23.45425066835742</v>
+        <v>23.58002398745769</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62222832591479</v>
+        <v>26.74800164501506</v>
       </c>
       <c r="E2" t="n">
-        <v>29.79020598347222</v>
+        <v>29.91597930257249</v>
       </c>
       <c r="F2" t="n">
-        <v>32.95818364102965</v>
+        <v>33.08395696012992</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.13394458500048</v>
+        <v>21.28666932962224</v>
       </c>
       <c r="C3" t="n">
-        <v>24.30192224255789</v>
+        <v>24.45464698717965</v>
       </c>
       <c r="D3" t="n">
-        <v>27.46989990011526</v>
+        <v>27.62262464473702</v>
       </c>
       <c r="E3" t="n">
-        <v>30.63787755767269</v>
+        <v>30.79060230229445</v>
       </c>
       <c r="F3" t="n">
-        <v>33.80585521523012</v>
+        <v>33.95857995985189</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21.98161615920095</v>
+        <v>22.1612923293442</v>
       </c>
       <c r="C4" t="n">
-        <v>25.14959381675836</v>
+        <v>25.32926998690161</v>
       </c>
       <c r="D4" t="n">
-        <v>28.31757147431574</v>
+        <v>28.49724764445898</v>
       </c>
       <c r="E4" t="n">
-        <v>31.48554913187316</v>
+        <v>31.66522530201641</v>
       </c>
       <c r="F4" t="n">
-        <v>34.6535267894306</v>
+        <v>34.83320295957385</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.82928773340143</v>
+        <v>23.03591532906616</v>
       </c>
       <c r="C5" t="n">
-        <v>25.99726539095884</v>
+        <v>26.20389298662357</v>
       </c>
       <c r="D5" t="n">
-        <v>29.16524304851621</v>
+        <v>29.37187064418094</v>
       </c>
       <c r="E5" t="n">
-        <v>32.33322070607364</v>
+        <v>32.53984830173837</v>
       </c>
       <c r="F5" t="n">
-        <v>35.50119836363108</v>
+        <v>35.70782595929581</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.6769593076019</v>
+        <v>23.91053832878812</v>
       </c>
       <c r="C6" t="n">
-        <v>26.84493696515931</v>
+        <v>27.07851598634554</v>
       </c>
       <c r="D6" t="n">
-        <v>30.01291462271668</v>
+        <v>30.24649364390291</v>
       </c>
       <c r="E6" t="n">
-        <v>33.18089228027411</v>
+        <v>33.41447130146034</v>
       </c>
       <c r="F6" t="n">
-        <v>36.34886993783154</v>
+        <v>36.58244895901777</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>28.26</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>28.32</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>28.34</v>
+        <v>28.52</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.35</v>
+        <v>26.54</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14427.13661050425</v>
+        <v>15171.29355729308</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6317417369869784</v>
+        <v>0.6643272052505156</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.54</v>
+        <v>26.56</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15171.29355729308</v>
+        <v>15249.62586748139</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6643272052505156</v>
+        <v>0.6677572545414148</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.56</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15249.62586748139</v>
+        <v>8684.507836309924</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6677572545414148</v>
+        <v>0.3802810088727439</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8684.507836309924</v>
+        <v>8684.507836309922</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.49724764445898</v>
+        <v>29.16437308125136</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29.34138963654237</v>
+        <v>30.12678795954584</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.2310346563339</v>
+        <v>27.72075076380965</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.486770770757503</v>
+        <v>1.484872320396618</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8684.507836309922</v>
+        <v>5781.613639220833</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3802810088727439</v>
+        <v>0.2535363226035737</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1557.497645946201</v>
+        <v>1583.96740558699</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1407.817600984264</v>
+        <v>1415.995282333736</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1330.389242982839</v>
+        <v>1387.97225410946</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3445.6014899133</v>
+        <v>3537.83194203019</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.34138963654237</v>
+        <v>30.12678795954584</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.34138963654237</v>
+        <v>30.12678795954584</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.01003338389682</v>
+        <v>24.62936192018939</v>
       </c>
       <c r="F11" t="n">
-        <v>18.98523869013281</v>
+        <v>19.47495479760857</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.2310346563339</v>
+        <v>27.72075076380965</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.41204632990028</v>
+        <v>20.94574667933413</v>
       </c>
       <c r="C2" t="n">
-        <v>23.58002398745769</v>
+        <v>24.18043688057079</v>
       </c>
       <c r="D2" t="n">
-        <v>26.74800164501506</v>
+        <v>27.41512708180744</v>
       </c>
       <c r="E2" t="n">
-        <v>29.91597930257249</v>
+        <v>30.64981728304408</v>
       </c>
       <c r="F2" t="n">
-        <v>33.08395696012992</v>
+        <v>33.88450748428075</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.28666932962224</v>
+        <v>21.82036967905609</v>
       </c>
       <c r="C3" t="n">
-        <v>24.45464698717965</v>
+        <v>25.05505988029275</v>
       </c>
       <c r="D3" t="n">
-        <v>27.62262464473702</v>
+        <v>28.2897500815294</v>
       </c>
       <c r="E3" t="n">
-        <v>30.79060230229445</v>
+        <v>31.52444028276604</v>
       </c>
       <c r="F3" t="n">
-        <v>33.95857995985189</v>
+        <v>34.7591304840027</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.1612923293442</v>
+        <v>22.69499267877805</v>
       </c>
       <c r="C4" t="n">
-        <v>25.32926998690161</v>
+        <v>25.92968288001471</v>
       </c>
       <c r="D4" t="n">
-        <v>28.49724764445898</v>
+        <v>29.16437308125136</v>
       </c>
       <c r="E4" t="n">
-        <v>31.66522530201641</v>
+        <v>32.399063282488</v>
       </c>
       <c r="F4" t="n">
-        <v>34.83320295957385</v>
+        <v>35.63375348372466</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.03591532906616</v>
+        <v>23.56961567850001</v>
       </c>
       <c r="C5" t="n">
-        <v>26.20389298662357</v>
+        <v>26.80430587973667</v>
       </c>
       <c r="D5" t="n">
-        <v>29.37187064418094</v>
+        <v>30.03899608097332</v>
       </c>
       <c r="E5" t="n">
-        <v>32.53984830173837</v>
+        <v>33.27368628220997</v>
       </c>
       <c r="F5" t="n">
-        <v>35.70782595929581</v>
+        <v>36.50837648344663</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.91053832878812</v>
+        <v>24.44423867822197</v>
       </c>
       <c r="C6" t="n">
-        <v>27.07851598634554</v>
+        <v>27.67892887945863</v>
       </c>
       <c r="D6" t="n">
-        <v>30.24649364390291</v>
+        <v>30.91361908069528</v>
       </c>
       <c r="E6" t="n">
-        <v>33.41447130146034</v>
+        <v>34.14830928193192</v>
       </c>
       <c r="F6" t="n">
-        <v>36.58244895901777</v>
+        <v>37.38299948316858</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>28.43</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>28.5</v>
+        <v>29.16</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>28.52</v>
+        <v>29.19</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5781.613639220833</v>
+        <v>5781.613639220832</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5781.613639220832</v>
+        <v>5781.613639220833</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.9</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5781.613639220833</v>
+        <v>10780.2511320494</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2535363226035737</v>
+        <v>0.4727374396347866</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.16437308125136</v>
+        <v>29.21540373512791</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.72075076380965</v>
+        <v>27.84832739850101</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.484872320396618</v>
+        <v>1.485484343530259</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10780.2511320494</v>
+        <v>10759.39064554938</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4727374396347866</v>
+        <v>0.4686359923040578</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="C2" t="n">
-        <v>35400</v>
+        <v>34900</v>
       </c>
       <c r="D2" t="n">
-        <v>1.636420478043209</v>
+        <v>1.615250550246618</v>
       </c>
       <c r="E2" t="n">
-        <v>1.554599454141048</v>
+        <v>1.534488022734287</v>
       </c>
       <c r="F2" t="n">
-        <v>1.514564475716336</v>
+        <v>1.494970965964774</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35200</v>
+        <v>35725</v>
       </c>
       <c r="C3" t="n">
-        <v>35200</v>
+        <v>35725</v>
       </c>
       <c r="D3" t="n">
-        <v>1.572339563507846</v>
+        <v>1.60396119126876</v>
       </c>
       <c r="E3" t="n">
-        <v>1.493722585332454</v>
+        <v>1.523763131705322</v>
       </c>
       <c r="F3" t="n">
-        <v>1.417778735304393</v>
+        <v>1.446291960090975</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30100</v>
+        <v>30675</v>
       </c>
       <c r="C4" t="n">
-        <v>30100</v>
+        <v>30675</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2398650859542</v>
+        <v>1.262691294073005</v>
       </c>
       <c r="E4" t="n">
-        <v>1.17787183165649</v>
+        <v>1.199556729369355</v>
       </c>
       <c r="F4" t="n">
-        <v>1.089195408323238</v>
+        <v>1.109247752206524</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29100</v>
+        <v>29675</v>
       </c>
       <c r="C5" t="n">
-        <v>29100</v>
+        <v>29675</v>
       </c>
       <c r="D5" t="n">
-        <v>1.165084981291423</v>
+        <v>1.187911189410229</v>
       </c>
       <c r="E5" t="n">
-        <v>1.106830732226852</v>
+        <v>1.128515629939717</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9971448038079749</v>
+        <v>1.016680747693439</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28100</v>
+        <v>28675</v>
       </c>
       <c r="C6" t="n">
-        <v>28100</v>
+        <v>28675</v>
       </c>
       <c r="D6" t="n">
-        <v>1.090304876628647</v>
+        <v>1.113131084747453</v>
       </c>
       <c r="E6" t="n">
-        <v>1.035789632797215</v>
+        <v>1.05747453051008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9091129336503116</v>
+        <v>0.9281457761807117</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27100</v>
+        <v>27675</v>
       </c>
       <c r="C7" t="n">
-        <v>27100</v>
+        <v>27675</v>
       </c>
       <c r="D7" t="n">
-        <v>1.015524771965871</v>
+        <v>1.038350980084677</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9647485333675773</v>
+        <v>0.9864334310804428</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8249538597624616</v>
+        <v>0.8434965571059223</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26600</v>
+        <v>27175</v>
       </c>
       <c r="C8" t="n">
-        <v>26600</v>
+        <v>27175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9740225753862243</v>
+        <v>0.9968487835050299</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9253214466169131</v>
+        <v>0.9470063443297784</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7708633805899471</v>
+        <v>0.7889285552595742</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26100</v>
+        <v>26675</v>
       </c>
       <c r="C9" t="n">
-        <v>26100</v>
+        <v>26675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9366325230548362</v>
+        <v>0.9594587311736419</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8898008969020944</v>
+        <v>0.9114857946149597</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7221823690464202</v>
+        <v>0.7397823184927843</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.245795966201083</v>
+        <v>8.367544632994704</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.62936192018939</v>
+        <v>24.63673236762325</v>
       </c>
       <c r="F11" t="n">
-        <v>19.47495479760857</v>
+        <v>19.48078276550631</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.72075076380965</v>
+        <v>27.84832739850101</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32450</v>
+        <v>32743.75</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.94574667933413</v>
+        <v>20.98146813704771</v>
       </c>
       <c r="C2" t="n">
-        <v>24.18043688057079</v>
+        <v>24.21615833828437</v>
       </c>
       <c r="D2" t="n">
-        <v>27.41512708180744</v>
+        <v>27.45084853952102</v>
       </c>
       <c r="E2" t="n">
-        <v>30.64981728304408</v>
+        <v>30.68553874075766</v>
       </c>
       <c r="F2" t="n">
-        <v>33.88450748428075</v>
+        <v>33.92022894199432</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.82036967905609</v>
+        <v>21.86374573485115</v>
       </c>
       <c r="C3" t="n">
-        <v>25.05505988029275</v>
+        <v>25.09843593608781</v>
       </c>
       <c r="D3" t="n">
-        <v>28.2897500815294</v>
+        <v>28.33312613732446</v>
       </c>
       <c r="E3" t="n">
-        <v>31.52444028276604</v>
+        <v>31.5678163385611</v>
       </c>
       <c r="F3" t="n">
-        <v>34.7591304840027</v>
+        <v>34.80250653979776</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.69499267877805</v>
+        <v>22.74602333265459</v>
       </c>
       <c r="C4" t="n">
-        <v>25.92968288001471</v>
+        <v>25.98071353389125</v>
       </c>
       <c r="D4" t="n">
-        <v>29.16437308125136</v>
+        <v>29.21540373512791</v>
       </c>
       <c r="E4" t="n">
-        <v>32.399063282488</v>
+        <v>32.45009393636454</v>
       </c>
       <c r="F4" t="n">
-        <v>35.63375348372466</v>
+        <v>35.68478413760121</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.56961567850001</v>
+        <v>23.62830093045803</v>
       </c>
       <c r="C5" t="n">
-        <v>26.80430587973667</v>
+        <v>26.8629911316947</v>
       </c>
       <c r="D5" t="n">
-        <v>30.03899608097332</v>
+        <v>30.09768133293135</v>
       </c>
       <c r="E5" t="n">
-        <v>33.27368628220997</v>
+        <v>33.33237153416798</v>
       </c>
       <c r="F5" t="n">
-        <v>36.50837648344663</v>
+        <v>36.56706173540465</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.44423867822197</v>
+        <v>24.51057852826148</v>
       </c>
       <c r="C6" t="n">
-        <v>27.67892887945863</v>
+        <v>27.74526872949814</v>
       </c>
       <c r="D6" t="n">
-        <v>30.91361908069528</v>
+        <v>30.97995893073479</v>
       </c>
       <c r="E6" t="n">
-        <v>34.14830928193192</v>
+        <v>34.21464913197143</v>
       </c>
       <c r="F6" t="n">
-        <v>37.38299948316858</v>
+        <v>37.44933933320809</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>29.1</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>29.16</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>29.19</v>
+        <v>29.24</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.09</v>
+        <v>28.14</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10759.39064554938</v>
+        <v>18761.26823955786</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4686359923040578</v>
+        <v>0.8171657529661958</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.21540373512791</v>
+        <v>29.66080744303116</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.12678795954584</v>
+        <v>30.63918760579404</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.84832739850101</v>
+        <v>28.19323719888684</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.485484343530259</v>
+        <v>1.484242622864504</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18761.26823955786</v>
+        <v>16990.18459410509</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8171657529661958</v>
+        <v>0.7414406565205618</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1583.96740558699</v>
+        <v>1594.710104465676</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1415.995282333736</v>
+        <v>1420.215554607629</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1387.97225410946</v>
+        <v>1433.181108709304</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3537.83194203019</v>
+        <v>3598.003767782608</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.12678795954584</v>
+        <v>30.63918760579404</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.12678795954584</v>
+        <v>30.63918760579404</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.63673236762325</v>
+        <v>25.07292892837553</v>
       </c>
       <c r="F11" t="n">
-        <v>19.48078276550631</v>
+        <v>19.82569256589214</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.84832739850101</v>
+        <v>28.19323719888684</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.98146813704771</v>
+        <v>21.33779110337035</v>
       </c>
       <c r="C2" t="n">
-        <v>24.21615833828437</v>
+        <v>24.6170216753973</v>
       </c>
       <c r="D2" t="n">
-        <v>27.45084853952102</v>
+        <v>27.89625224742427</v>
       </c>
       <c r="E2" t="n">
-        <v>30.68553874075766</v>
+        <v>31.17548281945124</v>
       </c>
       <c r="F2" t="n">
-        <v>33.92022894199432</v>
+        <v>34.45471339147823</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21.86374573485115</v>
+        <v>22.22006870117379</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09843593608781</v>
+        <v>25.49929927320075</v>
       </c>
       <c r="D3" t="n">
-        <v>28.33312613732446</v>
+        <v>28.77852984522772</v>
       </c>
       <c r="E3" t="n">
-        <v>31.5678163385611</v>
+        <v>32.05776041725468</v>
       </c>
       <c r="F3" t="n">
-        <v>34.80250653979776</v>
+        <v>35.33699098928167</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.74602333265459</v>
+        <v>23.10234629897723</v>
       </c>
       <c r="C4" t="n">
-        <v>25.98071353389125</v>
+        <v>26.38157687100419</v>
       </c>
       <c r="D4" t="n">
-        <v>29.21540373512791</v>
+        <v>29.66080744303116</v>
       </c>
       <c r="E4" t="n">
-        <v>32.45009393636454</v>
+        <v>32.94003801505813</v>
       </c>
       <c r="F4" t="n">
-        <v>35.68478413760121</v>
+        <v>36.21926858708511</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.62830093045803</v>
+        <v>23.98462389678068</v>
       </c>
       <c r="C5" t="n">
-        <v>26.8629911316947</v>
+        <v>27.26385446880763</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09768133293135</v>
+        <v>30.5430850408346</v>
       </c>
       <c r="E5" t="n">
-        <v>33.33237153416798</v>
+        <v>33.82231561286157</v>
       </c>
       <c r="F5" t="n">
-        <v>36.56706173540465</v>
+        <v>37.10154618488856</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.51057852826148</v>
+        <v>24.86690149458411</v>
       </c>
       <c r="C6" t="n">
-        <v>27.74526872949814</v>
+        <v>28.14613206661107</v>
       </c>
       <c r="D6" t="n">
-        <v>30.97995893073479</v>
+        <v>31.42536263863804</v>
       </c>
       <c r="E6" t="n">
-        <v>34.21464913197143</v>
+        <v>34.70459321066501</v>
       </c>
       <c r="F6" t="n">
-        <v>37.44933933320809</v>
+        <v>37.983823782692</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>29.15</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>29.22</v>
+        <v>29.66</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>29.24</v>
+        <v>29.68</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.14</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16990.18459410509</v>
+        <v>19444.60106771778</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7414406565205618</v>
+        <v>0.8485498024801457</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19444.60106771778</v>
+        <v>19444.60106771777</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19444.60106771777</v>
+        <v>19444.60106771778</v>
       </c>
     </row>
     <row r="16">

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.77</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19444.60106771778</v>
+        <v>19951.06795909816</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8485498024801457</v>
+        <v>0.8706516897416468</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.66080744303116</v>
+        <v>31.27690035145964</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30.63918760579404</v>
+        <v>32.39226519298419</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.19323719888684</v>
+        <v>29.60385308917282</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.484242622864504</v>
+        <v>1.48256466168766</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19951.06795909816</v>
+        <v>13930.73660641785</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8706516897416468</v>
+        <v>0.6062858230754276</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1594.710104465676</v>
+        <v>1548.782910774579</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1420.215554607629</v>
+        <v>1328.097192706979</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1433.181108709304</v>
+        <v>1389.146793215704</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>397.042</v>
+        <v>565.282</v>
       </c>
     </row>
     <row r="6">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.578</v>
+        <v>84.23099999999999</v>
       </c>
     </row>
     <row r="7">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-946.332</v>
+        <v>-1036.578</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-149.835</v>
+        <v>-142.424</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-195.556</v>
+        <v>-122.035</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3598.003767782608</v>
+        <v>3614.502896697262</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>117431435</v>
+        <v>111585370</v>
       </c>
     </row>
     <row r="13">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.63918760579404</v>
+        <v>32.39226519298419</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.63918760579404</v>
+        <v>32.39226519298419</v>
       </c>
     </row>
     <row r="15">
@@ -832,13 +832,13 @@
         <v>34900</v>
       </c>
       <c r="D2" t="n">
-        <v>1.615250550246618</v>
+        <v>1.654515596444229</v>
       </c>
       <c r="E2" t="n">
-        <v>1.534488022734287</v>
+        <v>1.571789816622018</v>
       </c>
       <c r="F2" t="n">
-        <v>1.494970965964774</v>
+        <v>1.531312141662706</v>
       </c>
     </row>
     <row r="3">
@@ -854,13 +854,13 @@
         <v>35725</v>
       </c>
       <c r="D3" t="n">
-        <v>1.60396119126876</v>
+        <v>1.64279505794532</v>
       </c>
       <c r="E3" t="n">
-        <v>1.523763131705322</v>
+        <v>1.560655305048054</v>
       </c>
       <c r="F3" t="n">
-        <v>1.446291960090975</v>
+        <v>1.481308461399916</v>
       </c>
     </row>
     <row r="4">
@@ -876,13 +876,13 @@
         <v>30675</v>
       </c>
       <c r="D4" t="n">
-        <v>1.262691294073005</v>
+        <v>1.289335672991899</v>
       </c>
       <c r="E4" t="n">
-        <v>1.199556729369355</v>
+        <v>1.224868889342304</v>
       </c>
       <c r="F4" t="n">
-        <v>1.109247752206524</v>
+        <v>1.132654278855953</v>
       </c>
     </row>
     <row r="5">
@@ -898,13 +898,13 @@
         <v>29675</v>
       </c>
       <c r="D5" t="n">
-        <v>1.187911189410229</v>
+        <v>1.212561137046908</v>
       </c>
       <c r="E5" t="n">
-        <v>1.128515629939717</v>
+        <v>1.151933080194563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.016680747693439</v>
+        <v>1.037777549724832</v>
       </c>
     </row>
     <row r="6">
@@ -920,13 +920,13 @@
         <v>28675</v>
       </c>
       <c r="D6" t="n">
-        <v>1.113131084747453</v>
+        <v>1.135786601101919</v>
       </c>
       <c r="E6" t="n">
-        <v>1.05747453051008</v>
+        <v>1.078997271046823</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9281457761807117</v>
+        <v>0.9470362932992423</v>
       </c>
     </row>
     <row r="7">
@@ -942,13 +942,13 @@
         <v>27675</v>
       </c>
       <c r="D7" t="n">
-        <v>1.038350980084677</v>
+        <v>1.059012065156929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9864334310804428</v>
+        <v>1.006061461899082</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8434965571059223</v>
+        <v>0.8602804331351009</v>
       </c>
     </row>
     <row r="8">
@@ -964,13 +964,13 @@
         <v>27175</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9968487835050299</v>
+        <v>1.016617775475405</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9470063443297784</v>
+        <v>0.9657868867016348</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7889285552595742</v>
+        <v>0.8045741802853558</v>
       </c>
     </row>
     <row r="9">
@@ -986,13 +986,13 @@
         <v>26675</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9594587311736419</v>
+        <v>0.9782305075029101</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9114857946149597</v>
+        <v>0.9293189821277645</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7397823184927843</v>
+        <v>0.7542561335344244</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.367544632994704</v>
+        <v>8.549199471897529</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25.07292892837553</v>
+        <v>26.62715726086176</v>
       </c>
       <c r="F11" t="n">
-        <v>19.82569256589214</v>
+        <v>21.05465361727529</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>28.19323719888684</v>
+        <v>29.60385308917282</v>
       </c>
     </row>
     <row r="13">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21.33779110337035</v>
+        <v>22.85590947453127</v>
       </c>
       <c r="C2" t="n">
-        <v>24.6170216753973</v>
+        <v>26.16083667691121</v>
       </c>
       <c r="D2" t="n">
-        <v>27.89625224742427</v>
+        <v>29.46576387929115</v>
       </c>
       <c r="E2" t="n">
-        <v>31.17548281945124</v>
+        <v>32.7706910816711</v>
       </c>
       <c r="F2" t="n">
-        <v>34.45471339147823</v>
+        <v>36.07561828405102</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22.22006870117379</v>
+        <v>23.76147771061552</v>
       </c>
       <c r="C3" t="n">
-        <v>25.49929927320075</v>
+        <v>27.06640491299546</v>
       </c>
       <c r="D3" t="n">
-        <v>28.77852984522772</v>
+        <v>30.3713321153754</v>
       </c>
       <c r="E3" t="n">
-        <v>32.05776041725468</v>
+        <v>33.67625931775535</v>
       </c>
       <c r="F3" t="n">
-        <v>35.33699098928167</v>
+        <v>36.98118652013527</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.10234629897723</v>
+        <v>24.66704594669977</v>
       </c>
       <c r="C4" t="n">
-        <v>26.38157687100419</v>
+        <v>27.97197314907971</v>
       </c>
       <c r="D4" t="n">
-        <v>29.66080744303116</v>
+        <v>31.27690035145964</v>
       </c>
       <c r="E4" t="n">
-        <v>32.94003801505813</v>
+        <v>34.5818275538396</v>
       </c>
       <c r="F4" t="n">
-        <v>36.21926858708511</v>
+        <v>37.88675475621952</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.98462389678068</v>
+        <v>25.57261418278402</v>
       </c>
       <c r="C5" t="n">
-        <v>27.26385446880763</v>
+        <v>28.87754138516395</v>
       </c>
       <c r="D5" t="n">
-        <v>30.5430850408346</v>
+        <v>32.18246858754389</v>
       </c>
       <c r="E5" t="n">
-        <v>33.82231561286157</v>
+        <v>35.48739578992384</v>
       </c>
       <c r="F5" t="n">
-        <v>37.10154618488856</v>
+        <v>38.79232299230377</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.86690149458411</v>
+        <v>26.47818241886826</v>
       </c>
       <c r="C6" t="n">
-        <v>28.14613206661107</v>
+        <v>29.78310962124821</v>
       </c>
       <c r="D6" t="n">
-        <v>31.42536263863804</v>
+        <v>33.08803682362814</v>
       </c>
       <c r="E6" t="n">
-        <v>34.70459321066501</v>
+        <v>36.39296402600809</v>
       </c>
       <c r="F6" t="n">
-        <v>37.983823782692</v>
+        <v>39.69789122838802</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>29.6</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>29.66</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>29.68</v>
+        <v>31.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.27690035145964</v>
+        <v>31.83692505039383</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.39226519298419</v>
+        <v>33.03827642069333</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.60385308917282</v>
+        <v>30.03489799494458</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.48256466168766</v>
+        <v>1.484293133099357</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13930.73660641785</v>
+        <v>11772.84173583345</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6062858230754276</v>
+        <v>0.5135222946158082</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1548.782910774579</v>
+        <v>1557.833114002742</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1328.097192706979</v>
+        <v>1388.955224014067</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1389.146793215704</v>
+        <v>1391.32396054853</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3614.502896697262</v>
+        <v>3686.588298565341</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.39226519298419</v>
+        <v>33.03827642069333</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.39226519298419</v>
+        <v>33.03827642069333</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>26.62715726086176</v>
+        <v>27.17228617635534</v>
       </c>
       <c r="F11" t="n">
-        <v>21.05465361727529</v>
+        <v>21.48569852304705</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>29.60385308917282</v>
+        <v>30.03489799494458</v>
       </c>
     </row>
     <row r="13">
@@ -1055,9 +1055,9 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22.85590947453127</v>
+        <v>23.30392923367863</v>
       </c>
       <c r="C2" t="n">
-        <v>26.16083667691121</v>
+        <v>26.66485890595195</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46576387929115</v>
+        <v>30.02578857822533</v>
       </c>
       <c r="E2" t="n">
-        <v>32.7706910816711</v>
+        <v>33.38671825049865</v>
       </c>
       <c r="F2" t="n">
-        <v>36.07561828405102</v>
+        <v>36.74764792277204</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23.76147771061552</v>
+        <v>24.20949746976288</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06640491299546</v>
+        <v>27.5704271420362</v>
       </c>
       <c r="D3" t="n">
-        <v>30.3713321153754</v>
+        <v>30.93135681430958</v>
       </c>
       <c r="E3" t="n">
-        <v>33.67625931775535</v>
+        <v>34.2922864865829</v>
       </c>
       <c r="F3" t="n">
-        <v>36.98118652013527</v>
+        <v>37.65321615885629</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24.66704594669977</v>
+        <v>25.11506570584712</v>
       </c>
       <c r="C4" t="n">
-        <v>27.97197314907971</v>
+        <v>28.47599537812045</v>
       </c>
       <c r="D4" t="n">
-        <v>31.27690035145964</v>
+        <v>31.83692505039383</v>
       </c>
       <c r="E4" t="n">
-        <v>34.5818275538396</v>
+        <v>35.19785472266715</v>
       </c>
       <c r="F4" t="n">
-        <v>37.88675475621952</v>
+        <v>38.55878439494054</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.57261418278402</v>
+        <v>26.02063394193137</v>
       </c>
       <c r="C5" t="n">
-        <v>28.87754138516395</v>
+        <v>29.3815636142047</v>
       </c>
       <c r="D5" t="n">
-        <v>32.18246858754389</v>
+        <v>32.74249328647808</v>
       </c>
       <c r="E5" t="n">
-        <v>35.48739578992384</v>
+        <v>36.10342295875139</v>
       </c>
       <c r="F5" t="n">
-        <v>38.79232299230377</v>
+        <v>39.46435263102478</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.47818241886826</v>
+        <v>26.92620217801562</v>
       </c>
       <c r="C6" t="n">
-        <v>29.78310962124821</v>
+        <v>30.28713185028895</v>
       </c>
       <c r="D6" t="n">
-        <v>33.08803682362814</v>
+        <v>33.64806152256233</v>
       </c>
       <c r="E6" t="n">
-        <v>36.39296402600809</v>
+        <v>37.00899119483564</v>
       </c>
       <c r="F6" t="n">
-        <v>39.69789122838802</v>
+        <v>40.36992086710903</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>31.21</v>
+        <v>31.77</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.28</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.3</v>
+        <v>31.86</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.83692505039383</v>
+        <v>32.09740808400806</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.03489799494458</v>
+        <v>30.68610557898015</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35300</v>
+        <v>31550</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.484293133099357</v>
+        <v>1.357376785320566</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11772.84173583345</v>
+        <v>11491.73082122701</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5135222946158082</v>
+        <v>0.492281862186855</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34900</v>
+        <v>38800</v>
       </c>
       <c r="C2" t="n">
-        <v>34900</v>
+        <v>38800</v>
       </c>
       <c r="D2" t="n">
-        <v>1.654515596444229</v>
+        <v>1.810148319622904</v>
       </c>
       <c r="E2" t="n">
-        <v>1.571789816622018</v>
+        <v>1.719640903641759</v>
       </c>
       <c r="F2" t="n">
-        <v>1.531312141662706</v>
+        <v>1.675355678729217</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35725</v>
+        <v>37250</v>
       </c>
       <c r="C3" t="n">
-        <v>35725</v>
+        <v>37250</v>
       </c>
       <c r="D3" t="n">
-        <v>1.64279505794532</v>
+        <v>1.762676332031699</v>
       </c>
       <c r="E3" t="n">
-        <v>1.560655305048054</v>
+        <v>1.674542515430114</v>
       </c>
       <c r="F3" t="n">
-        <v>1.481308461399916</v>
+        <v>1.589405417747995</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30675</v>
+        <v>25875</v>
       </c>
       <c r="C4" t="n">
-        <v>30675</v>
+        <v>25875</v>
       </c>
       <c r="D4" t="n">
-        <v>1.289335672991899</v>
+        <v>1.127011223559146</v>
       </c>
       <c r="E4" t="n">
-        <v>1.224868889342304</v>
+        <v>1.070660662381189</v>
       </c>
       <c r="F4" t="n">
-        <v>1.132654278855953</v>
+        <v>0.990055663100365</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29675</v>
+        <v>31225</v>
       </c>
       <c r="C5" t="n">
-        <v>29675</v>
+        <v>31225</v>
       </c>
       <c r="D5" t="n">
-        <v>1.212561137046908</v>
+        <v>1.270101968788561</v>
       </c>
       <c r="E5" t="n">
-        <v>1.151933080194563</v>
+        <v>1.206596870349133</v>
       </c>
       <c r="F5" t="n">
-        <v>1.037777549724832</v>
+        <v>1.087024207521741</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>28675</v>
+        <v>31250</v>
       </c>
       <c r="C6" t="n">
-        <v>28675</v>
+        <v>31250</v>
       </c>
       <c r="D6" t="n">
-        <v>1.135786601101919</v>
+        <v>1.243835941485878</v>
       </c>
       <c r="E6" t="n">
-        <v>1.078997271046823</v>
+        <v>1.181644144411583</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9470362932992423</v>
+        <v>1.037129491010306</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27675</v>
+        <v>31250</v>
       </c>
       <c r="C7" t="n">
-        <v>27675</v>
+        <v>31250</v>
       </c>
       <c r="D7" t="n">
-        <v>1.059012065156929</v>
+        <v>1.215947070391038</v>
       </c>
       <c r="E7" t="n">
-        <v>1.006061461899082</v>
+        <v>1.155149716871486</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8602804331351009</v>
+        <v>0.9877653964502757</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27175</v>
+        <v>30750</v>
       </c>
       <c r="C8" t="n">
-        <v>27175</v>
+        <v>30750</v>
       </c>
       <c r="D8" t="n">
-        <v>1.016617775475405</v>
+        <v>1.173552780709514</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9657868867016348</v>
+        <v>1.114875141674038</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8045741802853558</v>
+        <v>0.9287760742914536</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26675</v>
+        <v>30250</v>
       </c>
       <c r="C9" t="n">
-        <v>26675</v>
+        <v>30250</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9782305075029101</v>
+        <v>1.135165512737019</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9293189821277645</v>
+        <v>1.078407237100168</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7542561335344244</v>
+        <v>0.8752595058032369</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.549199471897529</v>
+        <v>9.17077143465459</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27.17228617635534</v>
+        <v>27.20976541313835</v>
       </c>
       <c r="F11" t="n">
-        <v>21.48569852304705</v>
+        <v>21.51533414432556</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30.03489799494458</v>
+        <v>30.68610557898015</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32743.75</v>
+        <v>33287.5</v>
       </c>
     </row>
   </sheetData>
@@ -1054,9 +1054,9 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.30392923367863</v>
+        <v>23.48626735720859</v>
       </c>
       <c r="C2" t="n">
-        <v>26.66485890595195</v>
+        <v>26.84719702948191</v>
       </c>
       <c r="D2" t="n">
-        <v>30.02578857822533</v>
+        <v>30.20812670175529</v>
       </c>
       <c r="E2" t="n">
-        <v>33.38671825049865</v>
+        <v>33.56905637402862</v>
       </c>
       <c r="F2" t="n">
-        <v>36.74764792277204</v>
+        <v>36.929986046302</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.20949746976288</v>
+        <v>24.43090804833497</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5704271420362</v>
+        <v>27.7918377206083</v>
       </c>
       <c r="D3" t="n">
-        <v>30.93135681430958</v>
+        <v>31.15276739288168</v>
       </c>
       <c r="E3" t="n">
-        <v>34.2922864865829</v>
+        <v>34.513697065155</v>
       </c>
       <c r="F3" t="n">
-        <v>37.65321615885629</v>
+        <v>37.87462673742838</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.11506570584712</v>
+        <v>25.37554873946135</v>
       </c>
       <c r="C4" t="n">
-        <v>28.47599537812045</v>
+        <v>28.73647841173468</v>
       </c>
       <c r="D4" t="n">
-        <v>31.83692505039383</v>
+        <v>32.09740808400806</v>
       </c>
       <c r="E4" t="n">
-        <v>35.19785472266715</v>
+        <v>35.45833775628138</v>
       </c>
       <c r="F4" t="n">
-        <v>38.55878439494054</v>
+        <v>38.81926742855477</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.02063394193137</v>
+        <v>26.32018943058773</v>
       </c>
       <c r="C5" t="n">
-        <v>29.3815636142047</v>
+        <v>29.68111910286106</v>
       </c>
       <c r="D5" t="n">
-        <v>32.74249328647808</v>
+        <v>33.04204877513444</v>
       </c>
       <c r="E5" t="n">
-        <v>36.10342295875139</v>
+        <v>36.40297844740776</v>
       </c>
       <c r="F5" t="n">
-        <v>39.46435263102478</v>
+        <v>39.76390811968115</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.92620217801562</v>
+        <v>27.26483012171412</v>
       </c>
       <c r="C6" t="n">
-        <v>30.28713185028895</v>
+        <v>30.62575979398744</v>
       </c>
       <c r="D6" t="n">
-        <v>33.64806152256233</v>
+        <v>33.98668946626083</v>
       </c>
       <c r="E6" t="n">
-        <v>37.00899119483564</v>
+        <v>37.34761913853414</v>
       </c>
       <c r="F6" t="n">
-        <v>40.36992086710903</v>
+        <v>40.70854881080753</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>31.77</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.84</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.86</v>
+        <v>32.12</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.09740808400806</v>
+        <v>31.88347831030685</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33.03827642069333</v>
+        <v>32.78466605483985</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.68610557898015</v>
+        <v>30.53169669350734</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.357376785320566</v>
+        <v>1.358392428076986</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11491.73082122701</v>
+        <v>12306.7207643724</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.492281862186855</v>
+        <v>0.5262518852407192</v>
       </c>
     </row>
   </sheetData>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1391.32396054853</v>
+        <v>1363.024754038932</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3686.588298565341</v>
+        <v>3658.289092055745</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.03827642069333</v>
+        <v>32.78466605483985</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33.03827642069333</v>
+        <v>32.78466605483985</v>
       </c>
     </row>
     <row r="15">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27.20976541313835</v>
+        <v>27.01448935917442</v>
       </c>
       <c r="F11" t="n">
-        <v>21.51533414432556</v>
+        <v>21.36092525885275</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30.68610557898015</v>
+        <v>30.53169669350734</v>
       </c>
     </row>
     <row r="13">
@@ -1054,10 +1054,10 @@
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.48626735720859</v>
+        <v>23.3151235382476</v>
       </c>
       <c r="C2" t="n">
-        <v>26.84719702948191</v>
+        <v>26.65466023315083</v>
       </c>
       <c r="D2" t="n">
-        <v>30.20812670175529</v>
+        <v>29.99419692805408</v>
       </c>
       <c r="E2" t="n">
-        <v>33.56905637402862</v>
+        <v>33.33373362295729</v>
       </c>
       <c r="F2" t="n">
-        <v>36.929986046302</v>
+        <v>36.67327031786051</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.43090804833497</v>
+        <v>24.25976422937399</v>
       </c>
       <c r="C3" t="n">
-        <v>27.7918377206083</v>
+        <v>27.59930092427721</v>
       </c>
       <c r="D3" t="n">
-        <v>31.15276739288168</v>
+        <v>30.93883761918046</v>
       </c>
       <c r="E3" t="n">
-        <v>34.513697065155</v>
+        <v>34.27837431408368</v>
       </c>
       <c r="F3" t="n">
-        <v>37.87462673742838</v>
+        <v>37.61791100898689</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.37554873946135</v>
+        <v>25.20440492050037</v>
       </c>
       <c r="C4" t="n">
-        <v>28.73647841173468</v>
+        <v>28.54394161540359</v>
       </c>
       <c r="D4" t="n">
-        <v>32.09740808400806</v>
+        <v>31.88347831030685</v>
       </c>
       <c r="E4" t="n">
-        <v>35.45833775628138</v>
+        <v>35.22301500521006</v>
       </c>
       <c r="F4" t="n">
-        <v>38.81926742855477</v>
+        <v>38.56255170011327</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.32018943058773</v>
+        <v>26.14904561162675</v>
       </c>
       <c r="C5" t="n">
-        <v>29.68111910286106</v>
+        <v>29.48858230652998</v>
       </c>
       <c r="D5" t="n">
-        <v>33.04204877513444</v>
+        <v>32.82811900143323</v>
       </c>
       <c r="E5" t="n">
-        <v>36.40297844740776</v>
+        <v>36.16765569633644</v>
       </c>
       <c r="F5" t="n">
-        <v>39.76390811968115</v>
+        <v>39.50719239123966</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.26483012171412</v>
+        <v>27.09368630275313</v>
       </c>
       <c r="C6" t="n">
-        <v>30.62575979398744</v>
+        <v>30.43322299765636</v>
       </c>
       <c r="D6" t="n">
-        <v>33.98668946626083</v>
+        <v>33.77275969255962</v>
       </c>
       <c r="E6" t="n">
-        <v>37.34761913853414</v>
+        <v>37.11229638746282</v>
       </c>
       <c r="F6" t="n">
-        <v>40.70854881080753</v>
+        <v>40.45183308236604</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>32.03</v>
+        <v>31.81</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>32.1</v>
+        <v>31.88</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>32.12</v>
+        <v>31.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.9</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12306.7207643724</v>
+        <v>8480.006604175454</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5262518852407192</v>
+        <v>0.3626164554915585</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.89</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8480.006604175454</v>
+        <v>12863.73276364781</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3626164554915585</v>
+        <v>0.5500704653753223</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.05</v>
+        <v>31.11</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12863.73276364781</v>
+        <v>20513.36422036326</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5500704653753223</v>
+        <v>0.8771789658905289</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.11</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20513.36422036326</v>
+        <v>18173.91382340659</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8771789658905289</v>
+        <v>0.777140929325199</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31.88347831030685</v>
+        <v>32.45933990809488</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.78466605483985</v>
+        <v>32.87731457333707</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30.53169669350734</v>
+        <v>31.83237791023157</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31550</v>
+        <v>35425</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.358392428076986</v>
+        <v>1.474623170493605</v>
       </c>
     </row>
     <row r="12">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18173.91382340659</v>
+        <v>17725.42995189072</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.777140929325199</v>
+        <v>0.7084878430974537</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1388.955224014067</v>
+        <v>1399.293443230531</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3658.289092055745</v>
+        <v>3668.627311272209</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.78466605483985</v>
+        <v>32.87731457333707</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.78466605483985</v>
+        <v>32.87731457333707</v>
       </c>
     </row>
     <row r="15">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38800</v>
+        <v>41313</v>
       </c>
       <c r="C2" t="n">
-        <v>38800</v>
+        <v>41313</v>
       </c>
       <c r="D2" t="n">
-        <v>1.810148319622904</v>
+        <v>1.886724908695468</v>
       </c>
       <c r="E2" t="n">
-        <v>1.719640903641759</v>
+        <v>1.792388663260694</v>
       </c>
       <c r="F2" t="n">
-        <v>1.675355678729217</v>
+        <v>1.746229994369363</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37250</v>
+        <v>42125</v>
       </c>
       <c r="C3" t="n">
-        <v>37250</v>
+        <v>42125</v>
       </c>
       <c r="D3" t="n">
-        <v>1.762676332031699</v>
+        <v>1.994451283129679</v>
       </c>
       <c r="E3" t="n">
-        <v>1.674542515430114</v>
+        <v>1.894728718973195</v>
       </c>
       <c r="F3" t="n">
-        <v>1.589405417747995</v>
+        <v>1.798396913395298</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25875</v>
+        <v>28725</v>
       </c>
       <c r="C4" t="n">
-        <v>25875</v>
+        <v>28725</v>
       </c>
       <c r="D4" t="n">
-        <v>1.127011223559146</v>
+        <v>1.246380400271111</v>
       </c>
       <c r="E4" t="n">
-        <v>1.070660662381189</v>
+        <v>1.184061380257555</v>
       </c>
       <c r="F4" t="n">
-        <v>0.990055663100365</v>
+        <v>1.094918974958152</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>31225</v>
+        <v>33625</v>
       </c>
       <c r="C5" t="n">
-        <v>31225</v>
+        <v>33625</v>
       </c>
       <c r="D5" t="n">
-        <v>1.270101968788561</v>
+        <v>1.427635623065999</v>
       </c>
       <c r="E5" t="n">
-        <v>1.206596870349133</v>
+        <v>1.356253841912699</v>
       </c>
       <c r="F5" t="n">
-        <v>1.087024207521741</v>
+        <v>1.221850308029458</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C6" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="D6" t="n">
-        <v>1.243835941485878</v>
+        <v>1.427549071397084</v>
       </c>
       <c r="E6" t="n">
-        <v>1.181644144411583</v>
+        <v>1.356171617827229</v>
       </c>
       <c r="F6" t="n">
-        <v>1.037129491010306</v>
+        <v>1.190312317267207</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="C7" t="n">
-        <v>31250</v>
+        <v>33625</v>
       </c>
       <c r="D7" t="n">
-        <v>1.215947070391038</v>
+        <v>1.427549071397084</v>
       </c>
       <c r="E7" t="n">
-        <v>1.155149716871486</v>
+        <v>1.356171617827229</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9877653964502757</v>
+        <v>1.159658679885871</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30750</v>
+        <v>33125</v>
       </c>
       <c r="C8" t="n">
-        <v>30750</v>
+        <v>33125</v>
       </c>
       <c r="D8" t="n">
-        <v>1.173552780709514</v>
+        <v>1.38515478171556</v>
       </c>
       <c r="E8" t="n">
-        <v>1.114875141674038</v>
+        <v>1.315897042629782</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9287760742914536</v>
+        <v>1.096242658698327</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30250</v>
+        <v>32625</v>
       </c>
       <c r="C9" t="n">
-        <v>30250</v>
+        <v>32625</v>
       </c>
       <c r="D9" t="n">
-        <v>1.135165512737019</v>
+        <v>1.346767513743065</v>
       </c>
       <c r="E9" t="n">
-        <v>1.078407237100168</v>
+        <v>1.279429138055912</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8752595058032369</v>
+        <v>1.038413390192283</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.17077143465459</v>
+        <v>10.34602323679596</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27.01448935917442</v>
+        <v>27.17311598908466</v>
       </c>
       <c r="F11" t="n">
-        <v>21.36092525885275</v>
+        <v>21.48635467343562</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30.53169669350734</v>
+        <v>31.83237791023157</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33287.5</v>
+        <v>36447</v>
       </c>
     </row>
   </sheetData>
@@ -1056,7 +1056,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.3151235382476</v>
+        <v>23.72658275788789</v>
       </c>
       <c r="C2" t="n">
-        <v>26.65466023315083</v>
+        <v>27.07447555397981</v>
       </c>
       <c r="D2" t="n">
-        <v>29.99419692805408</v>
+        <v>30.42236835007175</v>
       </c>
       <c r="E2" t="n">
-        <v>33.33373362295729</v>
+        <v>33.77026114616363</v>
       </c>
       <c r="F2" t="n">
-        <v>36.67327031786051</v>
+        <v>37.11815394225554</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.25976422937399</v>
+        <v>24.74506853689945</v>
       </c>
       <c r="C3" t="n">
-        <v>27.59930092427721</v>
+        <v>28.09296133299138</v>
       </c>
       <c r="D3" t="n">
-        <v>30.93883761918046</v>
+        <v>31.44085412908331</v>
       </c>
       <c r="E3" t="n">
-        <v>34.27837431408368</v>
+        <v>34.7887469251752</v>
       </c>
       <c r="F3" t="n">
-        <v>37.61791100898689</v>
+        <v>38.1366397212671</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.20440492050037</v>
+        <v>25.76355431591102</v>
       </c>
       <c r="C4" t="n">
-        <v>28.54394161540359</v>
+        <v>29.11144711200294</v>
       </c>
       <c r="D4" t="n">
-        <v>31.88347831030685</v>
+        <v>32.45933990809488</v>
       </c>
       <c r="E4" t="n">
-        <v>35.22301500521006</v>
+        <v>35.80723270418676</v>
       </c>
       <c r="F4" t="n">
-        <v>38.56255170011327</v>
+        <v>39.15512550027866</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.14904561162675</v>
+        <v>26.78204009492259</v>
       </c>
       <c r="C5" t="n">
-        <v>29.48858230652998</v>
+        <v>30.12993289101451</v>
       </c>
       <c r="D5" t="n">
-        <v>32.82811900143323</v>
+        <v>33.47782568710644</v>
       </c>
       <c r="E5" t="n">
-        <v>36.16765569633644</v>
+        <v>36.82571848319832</v>
       </c>
       <c r="F5" t="n">
-        <v>39.50719239123966</v>
+        <v>40.17361127929023</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.09368630275313</v>
+        <v>27.80052587393415</v>
       </c>
       <c r="C6" t="n">
-        <v>30.43322299765636</v>
+        <v>31.14841867002607</v>
       </c>
       <c r="D6" t="n">
-        <v>33.77275969255962</v>
+        <v>34.496311466118</v>
       </c>
       <c r="E6" t="n">
-        <v>37.11229638746282</v>
+        <v>37.84420426220989</v>
       </c>
       <c r="F6" t="n">
-        <v>40.45183308236604</v>
+        <v>41.1920970583018</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>31.81</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>31.88</v>
+        <v>32.46</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91</v>
+        <v>32.49</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/sblk_fv_report.xlsx
+++ b/outputs/sblk_fv_report.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.45933990809488</v>
+        <v>32.66636921042556</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.87731457333707</v>
+        <v>33.26791103372818</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31.83237791023157</v>
+        <v>31.26277162271943</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35425</v>
+        <v>37300</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.474623170493605</v>
+        <v>1.545803888086785</v>
       </c>
     </row>
     <row r="12">
@@ -552,7 +552,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>elevated</t>
+          <t>late-cycle/peak</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17725.42995189072</v>
+        <v>15279.63350641266</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7084878430974537</v>
+        <v>0.5841380162215315</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1399.293443230531</v>
+        <v>1414.349157448586</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1363.024754038932</v>
+        <v>1391.55389037431</v>
       </c>
     </row>
     <row r="5">
@@ -722,7 +722,7 @@
         <v/>
       </c>
       <c r="B11" t="n">
-        <v>3668.627311272209</v>
+        <v>3712.212161825641</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.87731457333707</v>
+        <v>33.26791103372818</v>
       </c>
     </row>
     <row r="14">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32.87731457333707</v>
+        <v>33.26791103372818</v>
       </c>
     </row>
     <row r="15">
@@ -826,19 +826,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41313</v>
+        <v>45250</v>
       </c>
       <c r="C2" t="n">
-        <v>41313</v>
+        <v>45250</v>
       </c>
       <c r="D2" t="n">
-        <v>1.886724908695468</v>
+        <v>2.057862401675058</v>
       </c>
       <c r="E2" t="n">
-        <v>1.792388663260694</v>
+        <v>1.954969281591305</v>
       </c>
       <c r="F2" t="n">
-        <v>1.746229994369363</v>
+        <v>1.904623739013762</v>
       </c>
     </row>
     <row r="3">
@@ -848,19 +848,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42125</v>
+        <v>44475</v>
       </c>
       <c r="C3" t="n">
-        <v>42125</v>
+        <v>44475</v>
       </c>
       <c r="D3" t="n">
-        <v>1.994451283129679</v>
+        <v>2.12785625548403</v>
       </c>
       <c r="E3" t="n">
-        <v>1.894728718973195</v>
+        <v>2.021463442709828</v>
       </c>
       <c r="F3" t="n">
-        <v>1.798396913395298</v>
+        <v>1.918688189769407</v>
       </c>
     </row>
     <row r="4">
@@ -870,19 +870,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28725</v>
+        <v>30125</v>
       </c>
       <c r="C4" t="n">
-        <v>28725</v>
+        <v>30125</v>
       </c>
       <c r="D4" t="n">
-        <v>1.246380400271111</v>
+        <v>1.35372851185599</v>
       </c>
       <c r="E4" t="n">
-        <v>1.184061380257555</v>
+        <v>1.28604208626319</v>
       </c>
       <c r="F4" t="n">
-        <v>1.094918974958152</v>
+        <v>1.189222033859465</v>
       </c>
     </row>
     <row r="5">
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33625</v>
+        <v>34359</v>
       </c>
       <c r="C5" t="n">
-        <v>33625</v>
+        <v>34359</v>
       </c>
       <c r="D5" t="n">
-        <v>1.427635623065999</v>
+        <v>1.465356122626111</v>
       </c>
       <c r="E5" t="n">
-        <v>1.356253841912699</v>
+        <v>1.392088316494806</v>
       </c>
       <c r="F5" t="n">
-        <v>1.221850308029458</v>
+        <v>1.254133618463789</v>
       </c>
     </row>
     <row r="6">
@@ -914,19 +914,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C6" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="D6" t="n">
-        <v>1.427549071397084</v>
+        <v>1.465331279091515</v>
       </c>
       <c r="E6" t="n">
-        <v>1.356171617827229</v>
+        <v>1.392064715136939</v>
       </c>
       <c r="F6" t="n">
-        <v>1.190312317267207</v>
+        <v>1.221815701699531</v>
       </c>
     </row>
     <row r="7">
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="C7" t="n">
-        <v>33625</v>
+        <v>34358</v>
       </c>
       <c r="D7" t="n">
-        <v>1.427549071397084</v>
+        <v>1.4652447274226</v>
       </c>
       <c r="E7" t="n">
-        <v>1.356171617827229</v>
+        <v>1.39198249105147</v>
       </c>
       <c r="F7" t="n">
-        <v>1.159658679885871</v>
+        <v>1.190280460656742</v>
       </c>
     </row>
     <row r="8">
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33125</v>
+        <v>33858</v>
       </c>
       <c r="C8" t="n">
-        <v>33125</v>
+        <v>33858</v>
       </c>
       <c r="D8" t="n">
-        <v>1.38515478171556</v>
+        <v>1.422850437741076</v>
       </c>
       <c r="E8" t="n">
-        <v>1.315897042629782</v>
+        <v>1.351707915854022</v>
       </c>
       <c r="F8" t="n">
-        <v>1.096242658698327</v>
+        <v>1.126075848987437</v>
       </c>
     </row>
     <row r="9">
@@ -980,19 +980,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32625</v>
+        <v>33358</v>
       </c>
       <c r="C9" t="n">
-        <v>32625</v>
+        <v>33358</v>
       </c>
       <c r="D9" t="n">
-        <v>1.346767513743065</v>
+        <v>1.384463169768581</v>
       </c>
       <c r="E9" t="n">
-        <v>1.279429138055912</v>
+        <v>1.315240011280152</v>
       </c>
       <c r="F9" t="n">
-        <v>1.038413390192283</v>
+        <v>1.067478298255135</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10.34602323679596</v>
+        <v>10.87231789070527</v>
       </c>
     </row>
     <row r="11">
@@ -1012,10 +1012,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>27.17311598908466</v>
+        <v>25.78716458660645</v>
       </c>
       <c r="F11" t="n">
-        <v>21.48635467343562</v>
+        <v>20.39045373201417</v>
       </c>
     </row>
     <row r="12">
@@ -1025,7 +1025,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>31.83237791023157</v>
+        <v>31.26277162271943</v>
       </c>
     </row>
     <row r="13">
@@ -1035,7 +1035,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36447</v>
+        <v>38552.25</v>
       </c>
     </row>
   </sheetData>
@@ -1099,19 +1099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.72658275788789</v>
+        <v>24.14398772872429</v>
       </c>
       <c r="C2" t="n">
-        <v>27.07447555397981</v>
+        <v>27.61656254805192</v>
       </c>
       <c r="D2" t="n">
-        <v>30.42236835007175</v>
+        <v>31.08913736737959</v>
       </c>
       <c r="E2" t="n">
-        <v>33.77026114616363</v>
+        <v>34.56171218670723</v>
       </c>
       <c r="F2" t="n">
-        <v>37.11815394225554</v>
+        <v>38.03428700603488</v>
       </c>
     </row>
     <row r="3">
@@ -1121,19 +1121,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24.74506853689945</v>
+        <v>24.93260365024728</v>
       </c>
       <c r="C3" t="n">
-        <v>28.09296133299138</v>
+        <v>28.4051784695749</v>
       </c>
       <c r="D3" t="n">
-        <v>31.44085412908331</v>
+        <v>31.87775328890257</v>
       </c>
       <c r="E3" t="n">
-        <v>34.7887469251752</v>
+        <v>35.35032810823022</v>
       </c>
       <c r="F3" t="n">
-        <v>38.1366397212671</v>
+        <v>38.82290292755786</v>
       </c>
     </row>
     <row r="4">
@@ -1143,19 +1143,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25.76355431591102</v>
+        <v>25.72121957177026</v>
       </c>
       <c r="C4" t="n">
-        <v>29.11144711200294</v>
+        <v>29.19379439109789</v>
       </c>
       <c r="D4" t="n">
-        <v>32.45933990809488</v>
+        <v>32.66636921042556</v>
       </c>
       <c r="E4" t="n">
-        <v>35.80723270418676</v>
+        <v>36.1389440297532</v>
       </c>
       <c r="F4" t="n">
-        <v>39.15512550027866</v>
+        <v>39.61151884908085</v>
       </c>
     </row>
     <row r="5">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.78204009492259</v>
+        <v>26.50983549329325</v>
       </c>
       <c r="C5" t="n">
-        <v>30.12993289101451</v>
+        <v>29.98241031262088</v>
       </c>
       <c r="D5" t="n">
-        <v>33.47782568710644</v>
+        <v>33.45498513194854</v>
       </c>
       <c r="E5" t="n">
-        <v>36.82571848319832</v>
+        <v>36.92755995127618</v>
       </c>
       <c r="F5" t="n">
-        <v>40.17361127929023</v>
+        <v>40.40013477060384</v>
       </c>
     </row>
     <row r="6">
@@ -1187,19 +1187,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.80052587393415</v>
+        <v>27.29845141481623</v>
       </c>
       <c r="C6" t="n">
-        <v>31.14841867002607</v>
+        <v>30.77102623414386</v>
       </c>
       <c r="D6" t="n">
-        <v>34.496311466118</v>
+        <v>34.24360105347153</v>
       </c>
       <c r="E6" t="n">
-        <v>37.84420426220989</v>
+        <v>37.71617587279917</v>
       </c>
       <c r="F6" t="n">
-        <v>41.1920970583018</v>
+        <v>41.18875069212682</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>32.38</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>32.46</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="4">
@@ -1253,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>32.49</v>
+        <v>32.69</v>
       </c>
     </row>
   </sheetData>
